--- a/task_center/task_manager.xlsx
+++ b/task_center/task_manager.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
   <si>
     <t>id</t>
   </si>
@@ -96,6 +96,12 @@
   </si>
   <si>
     <t>develop</t>
+  </si>
+  <si>
+    <t>cicd测试01</t>
+  </si>
+  <si>
+    <t>ywkk667</t>
   </si>
 </sst>
 </file>
@@ -1294,8 +1300,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultColWidth="7.375" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr defaultColWidth="7.375" defaultRowHeight="13.5" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="14" width="15.375" customWidth="1"/>
     <col min="15" max="16384" width="7.375" customWidth="1"/>
@@ -1409,6 +1415,38 @@
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
     </row>
+    <row r="4" ht="15" spans="1:14">
+      <c r="A4" s="2">
+        <v>106</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/task_center/task_manager.xlsx
+++ b/task_center/task_manager.xlsx
@@ -44,8 +44,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,7 +639,11 @@
           <t>cicd测试01</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>ywkk666</t>
@@ -668,6 +672,67 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>cicd测试01</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>88</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>https://github.com/ywkk666/cicd-test/pull/89</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>107</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>cicd测试02</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ywkk666</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>v1.0-beta</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>cicd-test-project</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>cicd测试02</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>90</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>feat/task-90</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>https://github.com/ywkk666/cicd-test/pull/91</t>
         </is>
       </c>
     </row>

--- a/task_center/task_manager.xlsx
+++ b/task_center/task_manager.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
   <si>
     <t>id</t>
   </si>
@@ -74,10 +74,10 @@
     <t>pr_url</t>
   </si>
   <si>
-    <t>新任务01</t>
-  </si>
-  <si>
-    <t>processing</t>
+    <t>cicd测试01</t>
+  </si>
+  <si>
+    <t>test</t>
   </si>
   <si>
     <t>ywkk666</t>
@@ -95,55 +95,79 @@
     <t>bug</t>
   </si>
   <si>
-    <t>测试04</t>
-  </si>
-  <si>
-    <t>feat/task-82</t>
-  </si>
-  <si>
-    <t>https://github.com/ywkk666/cicd-test/pull/83</t>
-  </si>
-  <si>
-    <t>新任务05</t>
+    <r>
+      <t>cicd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>测试</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>01</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>cicd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>测试</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>02</t>
+    </r>
+  </si>
+  <si>
+    <t>dev</t>
   </si>
   <si>
     <t>develop</t>
   </si>
   <si>
-    <t>feat/task-84</t>
-  </si>
-  <si>
-    <t>https://github.com/ywkk666/cicd-test/pull/85</t>
-  </si>
-  <si>
-    <t>cicd测试01</t>
-  </si>
-  <si>
-    <t>done</t>
-  </si>
-  <si>
-    <t>https://github.com/ywkk666/cicd-test/pull/89</t>
-  </si>
-  <si>
-    <t>cicd测试02</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>feat/task-90</t>
-  </si>
-  <si>
-    <t>https://github.com/ywkk666/cicd-test/pull/91</t>
-  </si>
-  <si>
-    <t>cicd测试03</t>
-  </si>
-  <si>
-    <t>cicd测试04</t>
-  </si>
-  <si>
-    <t>dev</t>
+    <r>
+      <t>cicd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>测试</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>03</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -156,7 +180,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -172,11 +196,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
+      <sz val="10.5"/>
+      <color rgb="FFCE9178"/>
+      <name val="Consolas"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -322,25 +345,19 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFCE9178"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FFC6EFCE"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -653,19 +670,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -674,7 +691,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -698,16 +715,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -716,89 +733,89 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -806,9 +823,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1155,13 +1175,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
+  <dimension ref="A1:O4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3"/>
   <cols>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="20.125" customWidth="1"/>
-    <col min="4" max="4" width="15.5" customWidth="1"/>
-    <col min="10" max="10" width="20.5" customWidth="1"/>
+    <col min="1" max="1" width="4.375" customWidth="1"/>
+    <col min="2" max="2" width="10.125" customWidth="1"/>
+    <col min="3" max="3" width="11.625" customWidth="1"/>
+    <col min="4" max="4" width="8.125" customWidth="1"/>
+    <col min="5" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="7" width="14.125" customWidth="1"/>
+    <col min="8" max="8" width="11.625" customWidth="1"/>
+    <col min="9" max="9" width="12.875" customWidth="1"/>
+    <col min="10" max="10" width="22.5" customWidth="1"/>
+    <col min="11" max="11" width="10.125" customWidth="1"/>
+    <col min="12" max="12" width="20.375" customWidth="1"/>
+    <col min="13" max="13" width="15.375" customWidth="1"/>
+    <col min="14" max="14" width="14.125" customWidth="1"/>
+    <col min="15" max="15" width="8.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -1211,227 +1241,92 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" ht="14.25" spans="1:15">
       <c r="A2">
-        <v>104</v>
-      </c>
-      <c r="B2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="3" t="s">
         <v>20</v>
       </c>
       <c r="K2" t="s">
         <v>21</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="M2">
-        <v>82</v>
-      </c>
-      <c r="N2" t="s">
+    </row>
+    <row r="3" ht="14.25" spans="1:15">
+      <c r="A3">
+        <v>102</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="O2" t="s">
+      <c r="C3" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3">
-        <v>105</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="E3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="H3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="3" t="s">
         <v>20</v>
       </c>
       <c r="K3" t="s">
         <v>21</v>
       </c>
-      <c r="L3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3">
-        <v>84</v>
-      </c>
-      <c r="N3" t="s">
-        <v>27</v>
-      </c>
-      <c r="O3" t="s">
-        <v>28</v>
+      <c r="L3" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" ht="14.25" spans="1:15">
       <c r="A4">
-        <v>106</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="G4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="3" t="s">
         <v>20</v>
       </c>
       <c r="K4" t="s">
         <v>21</v>
       </c>
-      <c r="L4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4">
-        <v>88</v>
-      </c>
-      <c r="O4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5">
-        <v>107</v>
-      </c>
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5">
-        <v>90</v>
-      </c>
-      <c r="N5" t="s">
-        <v>34</v>
-      </c>
-      <c r="O5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="3">
-        <v>108</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="3">
-        <v>109</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3" t="s">
+      <c r="L4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
